--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.174.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.174.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0174.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0174.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6 â€” 147</t>
+          <t>L72: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 69â€”70</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]167</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]167</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 7.</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L6: isolated marker/symbol line :: /</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]167</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -628,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • the English Orders</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,14 +670,10 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SUBPENA.â€” WRIT OF</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 70â€”71</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • the English Orders</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,13 +685,17 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L18: isolated marker/symbol line :: 0</t>
+          <t>L6: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 71 to 74</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -717,14 +725,10 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To appear and answer â€” form of</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ the English Orders</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -736,13 +740,17 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L22: symbol-only separator/garbage line :: , 112</t>
+          <t>L18: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 13 to 13</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -758,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -772,14 +780,10 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 65 â€”- 66</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 71 to 74</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -791,13 +795,17 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L24: isolated marker/symbol line :: 115</t>
+          <t>L22: symbol-only separator/garbage line :: , 112</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L157: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: •65</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -827,14 +835,10 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6â€”147</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 13 to 13</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -846,7 +850,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L26: symbol-only separator/garbage line :: . 116</t>
+          <t>L24: isolated marker/symbol line :: 115</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -882,26 +886,22 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Mode of service of SubpÃ¦ena.</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 71 to 74</t>
+          <t>L142: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L11: isolated marker/symbol line :: 167</t>
+          <t>L9: symbol-only separator/garbage line :: 6 — 147</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 70</t>
+          <t>L26: symbol-only separator/garbage line :: . 116</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -937,26 +937,22 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 26 â€” 27</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 49â€”50</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 26</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L15: isolated marker/symbol line :: 112</t>
+          <t>L11: isolated marker/symbol line :: 167</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: 71</t>
+          <t>L30: symbol-only separator/garbage line :: . 69—70</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -992,26 +988,22 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ na to amended Bill, may be served on Solicitor</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 13 to 13</t>
+          <t>L151: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L17: isolated marker/symbol line :: 115</t>
+          <t>L15: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L52: symbol-only separator/garbage line :: 7. 13</t>
+          <t>L32: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1033,12 +1025,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1047,26 +1039,22 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Form of Subp Ã¦ na to amended Bill</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L116: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SUBPÅ’NA.â€”WRIT OF</t>
+          <t>L153: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: 116</t>
+          <t>L17: isolated marker/symbol line :: 115</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 13</t>
+          <t>L34: symbol-only separator/garbage line :: . 70—71</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1093,7 +1081,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1105,19 +1093,19 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To appear and answerâ€”form of</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L23: symbol-only separator/garbage line :: 69-70</t>
+          <t>L19: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: e</t>
+          <t>L36: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1139,12 +1127,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1156,19 +1144,19 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L157: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: •65</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: 70</t>
+          <t>L23: symbol-only separator/garbage line :: 69-70</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L70: symbol-only separator/garbage line :: .15</t>
+          <t>L52: symbol-only separator/garbage line :: 7. 13</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1207,19 +1195,19 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ . 26</t>
+          <t>L177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L27: symbol-only separator/garbage line :: . 70-71</t>
+          <t>L25: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L74: symbol-only separator/garbage line :: . 110</t>
+          <t>L54: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1246,7 +1234,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1256,21 +1244,17 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 26â€”27</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: 71</t>
+          <t>L27: symbol-only separator/garbage line :: . 70-71</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L80: symbol-only separator/garbage line :: .73</t>
+          <t>L58: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1307,21 +1291,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L33: isolated marker/symbol line :: 48</t>
+          <t>L29: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L82: symbol-only separator/garbage line :: .48</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1358,21 +1338,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 48</t>
+          <t>L33: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 48</t>
+          <t>L70: symbol-only separator/garbage line :: .15</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1409,21 +1385,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 49</t>
+          <t>L34: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L86: symbol-only separator/garbage line :: .49</t>
+          <t>L74: symbol-only separator/garbage line :: . 110</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1448,21 +1420,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L157: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢65</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: 49</t>
+          <t>L35: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 49</t>
+          <t>L75: symbol-only separator/garbage line :: 6—147</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1487,21 +1455,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L161: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 65â€”66</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L37: symbol-only separator/garbage line :: 49-50</t>
+          <t>L36: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 49</t>
+          <t>L80: symbol-only separator/garbage line :: .73</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1526,21 +1490,17 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 49</t>
+          <t>L37: symbol-only separator/garbage line :: 49-50</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L94: symbol-only separator/garbage line :: .50</t>
+          <t>L82: symbol-only separator/garbage line :: .48</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1570,12 +1530,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 50</t>
+          <t>L38: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 50</t>
+          <t>L84: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1605,12 +1565,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 50</t>
+          <t>L39: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 3</t>
+          <t>L86: symbol-only separator/garbage line :: .49</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1640,12 +1600,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 109</t>
+          <t>L40: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L136: symbol-only separator/garbage line :: . 109</t>
+          <t>L88: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1675,12 +1635,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 111</t>
+          <t>L41: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: 111</t>
+          <t>L90: symbol-only separator/garbage line :: 49—50</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1710,12 +1670,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 73</t>
+          <t>L42: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 65</t>
+          <t>L92: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1745,12 +1705,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: '</t>
+          <t>L46: isolated marker/symbol line :: 73</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L94: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1780,12 +1740,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 4</t>
+          <t>L48: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L144: symbol-only separator/garbage line :: . 25</t>
+          <t>L96: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1815,12 +1775,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 3</t>
+          <t>L49: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 26</t>
+          <t>L98: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1850,12 +1810,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L63: symbol-only separator/garbage line :: . 25</t>
+          <t>L51: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L136: symbol-only separator/garbage line :: . 109</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1885,12 +1845,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 26</t>
+          <t>L63: symbol-only separator/garbage line :: . 25</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L137: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1920,12 +1880,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 65</t>
+          <t>L65: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L140: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1955,12 +1915,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: 65</t>
+          <t>L67: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L159: isolated marker/symbol line :: 65</t>
+          <t>L142: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1990,12 +1950,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 65</t>
+          <t>L68: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L163: isolated marker/symbol line :: 66</t>
+          <t>L144: symbol-only separator/garbage line :: . 25</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2025,12 +1985,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 66</t>
+          <t>L69: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L165: symbol-only separator/garbage line :: .66</t>
+          <t>L146: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2060,12 +2020,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L70: symbol-only separator/garbage line :: 65 —- 66</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L167: isolated marker/symbol line :: *</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 26</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2095,12 +2055,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 66</t>
+          <t>L71: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L169: isolated marker/symbol line :: 67</t>
+          <t>L149: symbol-only separator/garbage line :: 26—27</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2130,12 +2090,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 67</t>
+          <t>L72: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L171: symbol-only separator/garbage line :: . 108</t>
+          <t>L151: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2165,12 +2125,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: 108</t>
+          <t>L73: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L153: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2200,12 +2160,12 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L77: symbol-only separator/garbage line :: . 26</t>
+          <t>L74: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L179: isolated marker/symbol line :: ,</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2235,12 +2195,12 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 0</t>
+          <t>L75: isolated marker/symbol line :: 108</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L181: isolated marker/symbol line :: a</t>
+          <t>L157: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: •65</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2270,10 +2230,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 27</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L77: symbol-only separator/garbage line :: . 26</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L159: isolated marker/symbol line :: 65</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2301,10 +2265,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: ,</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L79: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L161: symbol-only separator/garbage line :: 65—66</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2332,10 +2300,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: 27</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L80: symbol-only separator/garbage line :: 26 — 27</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L163: isolated marker/symbol line :: 66</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2363,10 +2335,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: Â·</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L83: isolated marker/symbol line :: 27</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L165: symbol-only separator/garbage line :: .66</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2394,10 +2370,14 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 28</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="inlineStr"/>
+          <t>L86: isolated marker/symbol line :: ,</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>L167: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
       <c r="R45" s="1" t="inlineStr"/>
@@ -2425,10 +2405,14 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 28</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L87: isolated marker/symbol line :: 27</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L169: isolated marker/symbol line :: 67</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -2456,10 +2440,14 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 29</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L89: isolated marker/symbol line :: ·</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L171: symbol-only separator/garbage line :: . 108</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -2487,10 +2475,14 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 7</t>
-        </is>
-      </c>
-      <c r="O48" s="1" t="inlineStr"/>
+          <t>L90: isolated marker/symbol line :: 28</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>L177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr"/>
       <c r="R48" s="1" t="inlineStr"/>
@@ -2502,6 +2494,107 @@
       <c r="X48" s="1" t="inlineStr"/>
       <c r="Y48" s="1" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr"/>
+      <c r="B49" s="1" t="inlineStr"/>
+      <c r="C49" s="1" t="inlineStr"/>
+      <c r="D49" s="1" t="inlineStr"/>
+      <c r="E49" s="1" t="inlineStr"/>
+      <c r="F49" s="1" t="inlineStr"/>
+      <c r="G49" s="1" t="inlineStr"/>
+      <c r="H49" s="1" t="inlineStr"/>
+      <c r="I49" s="1" t="inlineStr"/>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
+      <c r="L49" s="1" t="inlineStr"/>
+      <c r="M49" s="1" t="inlineStr"/>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>L92: isolated marker/symbol line :: 28</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>L179: isolated marker/symbol line :: ,</t>
+        </is>
+      </c>
+      <c r="P49" s="1" t="inlineStr"/>
+      <c r="Q49" s="1" t="inlineStr"/>
+      <c r="R49" s="1" t="inlineStr"/>
+      <c r="S49" s="1" t="inlineStr"/>
+      <c r="T49" s="1" t="inlineStr"/>
+      <c r="U49" s="1" t="inlineStr"/>
+      <c r="V49" s="1" t="inlineStr"/>
+      <c r="W49" s="1" t="inlineStr"/>
+      <c r="X49" s="1" t="inlineStr"/>
+      <c r="Y49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr"/>
+      <c r="B50" s="1" t="inlineStr"/>
+      <c r="C50" s="1" t="inlineStr"/>
+      <c r="D50" s="1" t="inlineStr"/>
+      <c r="E50" s="1" t="inlineStr"/>
+      <c r="F50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr"/>
+      <c r="H50" s="1" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr"/>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
+      <c r="L50" s="1" t="inlineStr"/>
+      <c r="M50" s="1" t="inlineStr"/>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>L94: isolated marker/symbol line :: 29</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>L181: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
+      <c r="P50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="inlineStr"/>
+      <c r="R50" s="1" t="inlineStr"/>
+      <c r="S50" s="1" t="inlineStr"/>
+      <c r="T50" s="1" t="inlineStr"/>
+      <c r="U50" s="1" t="inlineStr"/>
+      <c r="V50" s="1" t="inlineStr"/>
+      <c r="W50" s="1" t="inlineStr"/>
+      <c r="X50" s="1" t="inlineStr"/>
+      <c r="Y50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" s="1" t="inlineStr"/>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" s="1" t="inlineStr"/>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr"/>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
+      <c r="L51" s="1" t="inlineStr"/>
+      <c r="M51" s="1" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>L98: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr"/>
+      <c r="R51" s="1" t="inlineStr"/>
+      <c r="S51" s="1" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr"/>
+      <c r="V51" s="1" t="inlineStr"/>
+      <c r="W51" s="1" t="inlineStr"/>
+      <c r="X51" s="1" t="inlineStr"/>
+      <c r="Y51" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
